--- a/artfynd/A 43389-2023 artfynd.xlsx
+++ b/artfynd/A 43389-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43389-2023 artfynd.xlsx
+++ b/artfynd/A 43389-2023 artfynd.xlsx
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">

--- a/artfynd/A 43389-2023 artfynd.xlsx
+++ b/artfynd/A 43389-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>67681776</v>
       </c>
       <c r="B2" t="n">
-        <v>91615</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,12 +797,7 @@
         <v>80420020</v>
       </c>
       <c r="B3" t="n">
-        <v>91615</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,15 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3056970</v>
+        <v>3017461</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,26 +936,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öststuga, Östra Rud, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>374358.8224201963</v>
+        <v>374359</v>
       </c>
       <c r="R4" t="n">
-        <v>6598960.508335972</v>
+        <v>6598961</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,27 +973,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-11-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-11-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>185 bladrosetter med 51 blomstänglar</t>
+          <t>ej räknad, noterad med 100 m noggranhet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,16 +995,6 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre barrskog med gran och tall</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1047,7 +1003,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Larsson, Elvi Eriksson</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
